--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-05-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-05-2025.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,7 +25,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,10 +47,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -62,7 +72,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -134,6 +144,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Price Tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £12.54</t>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £14.69</t>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £17.83</t>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £20.28</t>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £24.42</t>
+      </text>
+    </comment>
+    <comment ref="N7" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £26.72</t>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £26.94</t>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £29.49</t>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £32.88</t>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £34.00</t>
+      </text>
+    </comment>
+    <comment ref="N12" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £39.63</t>
+      </text>
+    </comment>
+    <comment ref="N13" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £40.56</t>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: Error: 'NoneType' object has no attribute 'find_all'</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.24</t>
+      </text>
+    </comment>
+    <comment ref="D16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.24</t>
+      </text>
+    </comment>
+    <comment ref="I17" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: Error: list index out of range</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,6 +527,9 @@
   </sheetPr>
   <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70.42578125" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3243,5 +3346,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>